--- a/file/tracking-list.xlsx
+++ b/file/tracking-list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAF33A3-4BAE-485E-9E51-AE36D7055AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D44A247-1C9A-448E-B6C2-1D33514F5FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="406">
   <si>
     <t>아크로리버하임</t>
   </si>
@@ -1230,6 +1230,42 @@
   </si>
   <si>
     <t>무지개마을대림</t>
+  </si>
+  <si>
+    <t>철산역 롯데캐슬&amp;SK VIEW 클래스티지</t>
+  </si>
+  <si>
+    <t>광명푸르지오포레나</t>
+  </si>
+  <si>
+    <t>롯데캐슬골드파크1차</t>
+  </si>
+  <si>
+    <t>철산래미안자이</t>
+  </si>
+  <si>
+    <t>신촌휴먼시아1단지</t>
+  </si>
+  <si>
+    <t>광명역센트럴자이(주상복합)</t>
+  </si>
+  <si>
+    <t>가산두산위브</t>
+  </si>
+  <si>
+    <t>주공1단지</t>
+  </si>
+  <si>
+    <t>주공8단지</t>
+  </si>
+  <si>
+    <t>남서울힐스테이트</t>
+  </si>
+  <si>
+    <t>광명역세권휴멍시아4단지</t>
+  </si>
+  <si>
+    <t>관악벽산타운5단지</t>
   </si>
 </sst>
 </file>
@@ -1673,10 +1709,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFC15EF-5188-42DD-AADD-57E027220B54}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B276"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -3789,6 +3825,102 @@
       </c>
       <c r="B264" s="12" t="s">
         <v>393</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="5">
+        <v>127424</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="4">
+        <v>133083</v>
+      </c>
+      <c r="B266" s="12" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="5">
+        <v>107929</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="5">
+        <v>25902</v>
+      </c>
+      <c r="B268" s="7" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="5">
+        <v>27821</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="5">
+        <v>111972</v>
+      </c>
+      <c r="B270" s="12" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="5">
+        <v>159</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="5">
+        <v>1627</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="4">
+        <v>1635</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="5">
+        <v>104347</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="4">
+        <v>100253</v>
+      </c>
+      <c r="B275" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="5">
+        <v>3359</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/file/tracking-list.xlsx
+++ b/file/tracking-list.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D44A247-1C9A-448E-B6C2-1D33514F5FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C9F818-678F-4FB7-92B4-D237F8444954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="418">
   <si>
     <t>아크로리버하임</t>
   </si>
@@ -1266,6 +1277,42 @@
   </si>
   <si>
     <t>관악벽산타운5단지</t>
+  </si>
+  <si>
+    <t>안안역푸르지오더샵</t>
+  </si>
+  <si>
+    <t>래미안안얀메가트리아</t>
+  </si>
+  <si>
+    <t>석수두산위브</t>
+  </si>
+  <si>
+    <t>석수역푸르지오</t>
+  </si>
+  <si>
+    <t>석수2차e편한세상</t>
+  </si>
+  <si>
+    <t>힐스테이트석수</t>
+  </si>
+  <si>
+    <t>석수e편한세상</t>
+  </si>
+  <si>
+    <t>안양어반포레자연앤e편한세상</t>
+  </si>
+  <si>
+    <t>안양씨엘포레자이</t>
+  </si>
+  <si>
+    <t>안양자이더포레스트</t>
+  </si>
+  <si>
+    <t>석수아이파크</t>
+  </si>
+  <si>
+    <t>한신휴플러스3차</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1374,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1350,13 +1397,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1394,6 +1452,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1412,9 +1473,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1452,7 +1513,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1558,7 +1619,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1700,7 +1761,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1709,7 +1770,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFC15EF-5188-42DD-AADD-57E027220B54}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B276"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="31.3984375" customWidth="1"/>
@@ -3923,6 +3984,102 @@
         <v>405</v>
       </c>
     </row>
+    <row r="277" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="13">
+        <v>147880</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="13">
+        <v>112054</v>
+      </c>
+      <c r="B278" s="12" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="13">
+        <v>8483</v>
+      </c>
+      <c r="B279" s="12" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="13">
+        <v>2004</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="13">
+        <v>19038</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="13">
+        <v>109366</v>
+      </c>
+      <c r="B282" s="12" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="13">
+        <v>3090</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="13">
+        <v>147085</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="13">
+        <v>121645</v>
+      </c>
+      <c r="B285" s="12" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="13">
+        <v>174657</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="13">
+        <v>25775</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="13">
+        <v>101284</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>417</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/file/tracking-list.xlsx
+++ b/file/tracking-list.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C9F818-678F-4FB7-92B4-D237F8444954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50D25BB-F57C-42F4-9E5B-BB20564C3D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
+    <workbookView xWindow="43200" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="430">
   <si>
     <t>아크로리버하임</t>
   </si>
@@ -1313,6 +1302,42 @@
   </si>
   <si>
     <t>한신휴플러스3차</t>
+  </si>
+  <si>
+    <t>광장힐스테이트</t>
+  </si>
+  <si>
+    <t>광장현대5단지</t>
+  </si>
+  <si>
+    <t>현대8단지</t>
+  </si>
+  <si>
+    <t>현대프라임</t>
+  </si>
+  <si>
+    <t>구의현대2단지</t>
+  </si>
+  <si>
+    <t>e편한세상광진그랜드파크</t>
+  </si>
+  <si>
+    <t>롯데캐슬이스트폴</t>
+  </si>
+  <si>
+    <t>롯데캐슬리버파크시그니처</t>
+  </si>
+  <si>
+    <t>우성1차</t>
+  </si>
+  <si>
+    <t>자양우성3차</t>
+  </si>
+  <si>
+    <t>자양하늘채베르</t>
+  </si>
+  <si>
+    <t>래미안파크스위트</t>
   </si>
 </sst>
 </file>
@@ -1473,9 +1498,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1513,7 +1538,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1619,7 +1644,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1761,7 +1786,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1770,7 +1795,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFC15EF-5188-42DD-AADD-57E027220B54}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="31.3984375" customWidth="1"/>
@@ -4080,6 +4105,102 @@
         <v>417</v>
       </c>
     </row>
+    <row r="289" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="13">
+        <v>100514</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="13">
+        <v>75</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="13">
+        <v>76</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="13">
+        <v>84</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="13">
+        <v>81</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="13">
+        <v>125105</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="13">
+        <v>160239</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="13">
+        <v>135887</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="13">
+        <v>90</v>
+      </c>
+      <c r="B297" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="13">
+        <v>93</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="13">
+        <v>140746</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="13">
+        <v>112339</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/file/tracking-list.xlsx
+++ b/file/tracking-list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50D25BB-F57C-42F4-9E5B-BB20564C3D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867877FE-04DB-4C65-85B1-EBA73FC293CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43200" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="430">
   <si>
     <t>아크로리버하임</t>
   </si>
@@ -1439,7 +1439,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1479,6 +1479,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1795,7 +1798,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFC15EF-5188-42DD-AADD-57E027220B54}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B311"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="31.3984375" customWidth="1"/>
@@ -4201,6 +4204,94 @@
         <v>429</v>
       </c>
     </row>
+    <row r="301" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="8">
+        <v>75</v>
+      </c>
+      <c r="B301" s="14" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="8">
+        <v>76</v>
+      </c>
+      <c r="B302" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="8">
+        <v>84</v>
+      </c>
+      <c r="B303" s="11" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="8">
+        <v>81</v>
+      </c>
+      <c r="B304" s="11" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A305" s="8">
+        <v>125105</v>
+      </c>
+      <c r="B305" s="11" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="8">
+        <v>160239</v>
+      </c>
+      <c r="B306" s="11" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A307" s="8">
+        <v>135887</v>
+      </c>
+      <c r="B307" s="11" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="8">
+        <v>90</v>
+      </c>
+      <c r="B308" s="11" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="8">
+        <v>93</v>
+      </c>
+      <c r="B309" s="11" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A310" s="8">
+        <v>140746</v>
+      </c>
+      <c r="B310" s="11" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="8">
+        <v>112339</v>
+      </c>
+      <c r="B311" s="14" t="s">
+        <v>429</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
